--- a/artfynd/A 66349-2021 artfynd.xlsx
+++ b/artfynd/A 66349-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1445,6 +1445,131 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>113502760</v>
+      </c>
+      <c r="B8" t="n">
+        <v>109414</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219716</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Krusfrö</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Selinum carvifolia</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Orrmossen (krusfrö), Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>571044</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6620508</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>U-Sur-0499</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>680/970 (10)</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Bo Eriksson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 66349-2021 artfynd.xlsx
+++ b/artfynd/A 66349-2021 artfynd.xlsx
@@ -1450,7 +1450,7 @@
         <v>113502760</v>
       </c>
       <c r="B8" t="n">
-        <v>109414</v>
+        <v>109436</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 66349-2021 artfynd.xlsx
+++ b/artfynd/A 66349-2021 artfynd.xlsx
@@ -1450,7 +1450,7 @@
         <v>113502760</v>
       </c>
       <c r="B8" t="n">
-        <v>109436</v>
+        <v>109440</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 66349-2021 artfynd.xlsx
+++ b/artfynd/A 66349-2021 artfynd.xlsx
@@ -1450,7 +1450,7 @@
         <v>113502760</v>
       </c>
       <c r="B8" t="n">
-        <v>109440</v>
+        <v>109446</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 66349-2021 artfynd.xlsx
+++ b/artfynd/A 66349-2021 artfynd.xlsx
@@ -1450,7 +1450,7 @@
         <v>113502760</v>
       </c>
       <c r="B8" t="n">
-        <v>109446</v>
+        <v>109453</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 66349-2021 artfynd.xlsx
+++ b/artfynd/A 66349-2021 artfynd.xlsx
@@ -1450,7 +1450,7 @@
         <v>113502760</v>
       </c>
       <c r="B8" t="n">
-        <v>109453</v>
+        <v>109458</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 66349-2021 artfynd.xlsx
+++ b/artfynd/A 66349-2021 artfynd.xlsx
@@ -1450,7 +1450,7 @@
         <v>113502760</v>
       </c>
       <c r="B8" t="n">
-        <v>109458</v>
+        <v>109488</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 66349-2021 artfynd.xlsx
+++ b/artfynd/A 66349-2021 artfynd.xlsx
@@ -1450,7 +1450,7 @@
         <v>113502760</v>
       </c>
       <c r="B8" t="n">
-        <v>109488</v>
+        <v>109502</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 66349-2021 artfynd.xlsx
+++ b/artfynd/A 66349-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 66349-2021 artfynd.xlsx
+++ b/artfynd/A 66349-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1447,10 +1447,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113502760</v>
+        <v>114406631</v>
       </c>
       <c r="B8" t="n">
-        <v>109766</v>
+        <v>5165</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1459,49 +1459,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219716</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Krusfrö</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Selinum carvifolia</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Orrmossen (krusfrö), Vstm</t>
+          <t>Orrmossen, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571044</v>
+        <v>570910</v>
       </c>
       <c r="R8" t="n">
-        <v>6620508</v>
+        <v>6620581</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1523,24 +1524,24 @@
           <t>Sura</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>U-Sur-0499</t>
-        </is>
-      </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2024-01-26</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>680/970 (10)</t>
+          <t>2024-01-26</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1553,10 +1554,20 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Bryn med gammal blandskog, gran, tall, björk, dikad mosse</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Torrgran</t>
+        </is>
+      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bo Eriksson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -1564,70 +1575,73 @@
           <t>Tom Sävström</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>114406631</v>
+        <v>115688694</v>
       </c>
       <c r="B9" t="n">
-        <v>5165</v>
+        <v>57414</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Orrmossen, Vstm</t>
+          <t>Orrmossen, Täkten, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>570910</v>
+        <v>570958</v>
       </c>
       <c r="R9" t="n">
-        <v>6620581</v>
+        <v>6620648</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1651,22 +1665,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-01-26</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-01-26</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1675,19 +1689,8 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Bryn med gammal blandskog, gran, tall, björk, dikad mosse</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Torrgran</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1701,258 +1704,6 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>115688673</v>
-      </c>
-      <c r="B10" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Orrmossen, Täkten, Vstm</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>570958</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6620648</v>
-      </c>
-      <c r="S10" t="n">
-        <v>100</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Surahammar</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Sura</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2024-04-05</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2024-04-05</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>115688694</v>
-      </c>
-      <c r="B11" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Orrmossen, Täkten, Vstm</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>570958</v>
-      </c>
-      <c r="R11" t="n">
-        <v>6620648</v>
-      </c>
-      <c r="S11" t="n">
-        <v>100</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Surahammar</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Sura</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2024-04-05</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2024-04-05</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 66349-2021 artfynd.xlsx
+++ b/artfynd/A 66349-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1705,6 +1705,134 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>125546589</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57440</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>102118</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Nattskärra</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Caprimulgus europaeus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Orrmossen, Täkten, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>570958</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6620648</v>
+      </c>
+      <c r="S10" t="n">
+        <v>100</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>23:05</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>23:05</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 66349-2021 artfynd.xlsx
+++ b/artfynd/A 66349-2021 artfynd.xlsx
@@ -1710,12 +1710,7 @@
         <v>125546589</v>
       </c>
       <c r="B10" t="n">
-        <v>57440</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57453</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 66349-2021 artfynd.xlsx
+++ b/artfynd/A 66349-2021 artfynd.xlsx
@@ -1710,7 +1710,7 @@
         <v>125546589</v>
       </c>
       <c r="B10" t="n">
-        <v>57453</v>
+        <v>57454</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 66349-2021 artfynd.xlsx
+++ b/artfynd/A 66349-2021 artfynd.xlsx
@@ -1710,7 +1710,7 @@
         <v>125546589</v>
       </c>
       <c r="B10" t="n">
-        <v>57454</v>
+        <v>57458</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 66349-2021 artfynd.xlsx
+++ b/artfynd/A 66349-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102312338</v>
+        <v>114406631</v>
       </c>
       <c r="B2" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,27 +686,32 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223597</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571014.4066957255</v>
+        <v>570910</v>
       </c>
       <c r="R2" t="n">
-        <v>6620518.085080126</v>
+        <v>6620581</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
+          <t>2024-01-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
+          <t>2024-01-26</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +779,12 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Vägdike</t>
+          <t>Bryn med gammal blandskog, gran, tall, björk, dikad mosse</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Torrgran</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,15 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102312242</v>
+        <v>132310057</v>
       </c>
       <c r="B3" t="n">
-        <v>108203</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58519</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,50 +813,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219716</v>
+        <v>102990</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Krusfrö</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Selinum carvifolia</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Orrmossen, Vstm</t>
+          <t>Orrmossen, Orrmossen, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571044.4294509736</v>
+        <v>570805</v>
       </c>
       <c r="R3" t="n">
-        <v>6620507.555368075</v>
+        <v>6620606</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,22 +875,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,61 +899,50 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Grusmark, vägren</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Andreas Lundqvist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Andreas Lundqvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>102312328</v>
+        <v>134320509</v>
       </c>
       <c r="B4" t="n">
-        <v>108203</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58107</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219716</v>
+        <v>205976</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Krusfrö</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Selinum carvifolia</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -969,17 +950,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -987,13 +964,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571014.4066957255</v>
+        <v>570837</v>
       </c>
       <c r="R4" t="n">
-        <v>6620518.085080126</v>
+        <v>6620576</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1017,22 +994,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>05:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>05:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,86 +1018,82 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Vägren</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Daniel Hjelm</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Daniel Hjelm</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105868207</v>
+        <v>102312242</v>
       </c>
       <c r="B5" t="n">
-        <v>8367</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111399</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>219716</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Krusfrö</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Selinum carvifolia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>(L.) L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Orrmossen, Täkten, Vstm</t>
+          <t>Orrmossen, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570957.8479657174</v>
+        <v>571044</v>
       </c>
       <c r="R5" t="n">
-        <v>6620648.202238731</v>
+        <v>6620508</v>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1144,22 +1117,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-01-05</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-01-05</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1174,12 +1137,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Tallmosse, skvattram</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Björk</t>
+          <t>Grusmark, vägren</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1197,15 +1155,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>108071873</v>
+        <v>102312328</v>
       </c>
       <c r="B6" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>111399</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,21 +1166,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>219716</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Krusfrö</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Selinum carvifolia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1235,27 +1188,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Orrmossen, Täkten, Vstm</t>
+          <t>Orrmossen, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570957.8479657174</v>
+        <v>571014</v>
       </c>
       <c r="R6" t="n">
-        <v>6620648.202238731</v>
+        <v>6620518</v>
       </c>
       <c r="S6" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1279,22 +1236,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-04-12</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-04-12</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1303,8 +1250,14 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Vägren</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1321,15 +1274,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110896252</v>
+        <v>102312627</v>
       </c>
       <c r="B7" t="n">
-        <v>108228</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111399</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,8 +1302,16 @@
           <t>(L.) L.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -1369,13 +1325,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570959.4336584168</v>
+        <v>571089</v>
       </c>
       <c r="R7" t="n">
-        <v>6620538.232379696</v>
+        <v>6620489</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1399,22 +1355,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1429,7 +1375,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Vägkanter</t>
+          <t>Vägren</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1447,48 +1393,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>114406631</v>
+        <v>110896252</v>
       </c>
       <c r="B8" t="n">
-        <v>5165</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111399</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>219716</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Krusfrö</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Selinum carvifolia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1496,13 +1436,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>570910</v>
+        <v>570959</v>
       </c>
       <c r="R8" t="n">
-        <v>6620581</v>
+        <v>6620538</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1526,22 +1466,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-01-26</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:10</t>
+          <t>2023-07-17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-01-26</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:10</t>
+          <t>2023-07-17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1556,12 +1486,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Bryn med gammal blandskog, gran, tall, björk, dikad mosse</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Torrgran</t>
+          <t>Vägkanter</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1579,69 +1504,52 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115688694</v>
+        <v>102312338</v>
       </c>
       <c r="B9" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99038</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>223597</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Orrmossen, Täkten, Vstm</t>
+          <t>Orrmossen, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>570958</v>
+        <v>571014</v>
       </c>
       <c r="R9" t="n">
-        <v>6620648</v>
+        <v>6620518</v>
       </c>
       <c r="S9" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1665,22 +1573,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1689,8 +1587,14 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Vägdike</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1704,248 +1608,6 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>125546589</v>
-      </c>
-      <c r="B10" t="n">
-        <v>57458</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>102118</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Nattskärra</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Caprimulgus europaeus</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Orrmossen, Täkten, Vstm</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>570958</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6620648</v>
-      </c>
-      <c r="S10" t="n">
-        <v>100</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Surahammar</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Sura</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2025-05-29</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>23:05</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2025-05-29</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>23:05</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>134320509</v>
-      </c>
-      <c r="B11" t="n">
-        <v>58107</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>205976</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Gråkråka</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Corvus corone cornix</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Orrmossen, Vstm</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>570837</v>
-      </c>
-      <c r="R11" t="n">
-        <v>6620576</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Surahammar</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Sura</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>05:33</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>05:34</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Daniel Hjelm</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Daniel Hjelm</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 66349-2021 artfynd.xlsx
+++ b/artfynd/A 66349-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -917,32 +917,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134320509</v>
+        <v>134682971</v>
       </c>
       <c r="B4" t="n">
-        <v>58107</v>
+        <v>43290</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205976</v>
+        <v>201143</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Ängsblåvinge</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Cyaniris semiargus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Rottemburg, 1775)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -950,11 +950,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -964,13 +969,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570837</v>
+        <v>570959</v>
       </c>
       <c r="R4" t="n">
-        <v>6620576</v>
+        <v>6620538</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,22 +999,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>05:33</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>05:34</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,68 +1023,75 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Örtrika vägkanter, skogsbilväg</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>102312242</v>
+        <v>134683037</v>
       </c>
       <c r="B5" t="n">
-        <v>111399</v>
+        <v>43314</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219716</v>
+        <v>201146</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Krusfrö</t>
+          <t>Silverblåvinge</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Selinum carvifolia</t>
+          <t>Polyommatus amandus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) L.</t>
+          <t>(Schneider, 1792)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1087,10 +1099,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571044</v>
+        <v>570959</v>
       </c>
       <c r="R5" t="n">
-        <v>6620508</v>
+        <v>6620538</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1117,12 +1129,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,7 +1159,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Grusmark, vägren</t>
+          <t>Örtrika vägkanter, skogsbilväg</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1155,32 +1177,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102312328</v>
+        <v>134320509</v>
       </c>
       <c r="B6" t="n">
-        <v>111399</v>
+        <v>58107</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219716</v>
+        <v>205976</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Krusfrö</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Selinum carvifolia</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1188,17 +1210,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1206,13 +1224,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571014</v>
+        <v>570837</v>
       </c>
       <c r="R6" t="n">
-        <v>6620518</v>
+        <v>6620576</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1236,12 +1254,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>05:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>05:34</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,31 +1278,25 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Vägren</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Daniel Hjelm</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Daniel Hjelm</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>102312627</v>
+        <v>102312242</v>
       </c>
       <c r="B7" t="n">
         <v>111399</v>
@@ -1304,7 +1326,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1325,13 +1347,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571089</v>
+        <v>571044</v>
       </c>
       <c r="R7" t="n">
-        <v>6620489</v>
+        <v>6620508</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1375,7 +1397,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Vägren</t>
+          <t>Grusmark, vägren</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1393,7 +1415,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110896252</v>
+        <v>102312328</v>
       </c>
       <c r="B8" t="n">
         <v>111399</v>
@@ -1421,8 +1443,16 @@
           <t>(L.) L.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -1436,10 +1466,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>570959</v>
+        <v>571014</v>
       </c>
       <c r="R8" t="n">
-        <v>6620538</v>
+        <v>6620518</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1466,12 +1496,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,7 +1516,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Vägkanter</t>
+          <t>Vägren</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1504,32 +1534,44 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>102312338</v>
+        <v>102312627</v>
       </c>
       <c r="B9" t="n">
-        <v>99038</v>
+        <v>111399</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>223597</v>
+        <v>219716</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Krusfrö</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>Selinum carvifolia</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -1543,13 +1585,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571014</v>
+        <v>571089</v>
       </c>
       <c r="R9" t="n">
-        <v>6620518</v>
+        <v>6620489</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1593,7 +1635,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Vägdike</t>
+          <t>Vägren</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1608,6 +1650,224 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>110896252</v>
+      </c>
+      <c r="B10" t="n">
+        <v>111399</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219716</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Krusfrö</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Selinum carvifolia</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Orrmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>570959</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6620538</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Vägkanter</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>102312338</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Orrmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>571014</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6620518</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Vägdike</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 66349-2021 artfynd.xlsx
+++ b/artfynd/A 66349-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -799,6 +804,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114406631</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,6 +924,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132310057</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1044,6 +1059,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682971</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1174,6 +1194,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134683037</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1293,6 +1318,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134320509</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1412,6 +1442,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102312242</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1531,6 +1566,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102312328</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1650,6 +1690,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102312627</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1761,6 +1806,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110896252</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1868,8 +1918,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102312338</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>